--- a/97_Mockup/Wire_Frame.xlsx
+++ b/97_Mockup/Wire_Frame.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\97_Mockup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77D9995-7E43-45F9-8FC5-D66CC3DF8B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD1580E-CE9B-48FB-A6A1-7D1CBBE4A881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{78629192-825E-4083-940A-C6F0AB98E91E}"/>
   </bookViews>
@@ -243,14 +243,6 @@
     <rPh sb="5" eb="7">
       <t>ニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>○○ディレクトリ２</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>○○ディレクトリ１</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4263,6 +4255,14 @@
     <rPh sb="4" eb="6">
       <t>ジコク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○○ディレクトリ１リンク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○○ディレクトリ２リンク</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5826,8 +5826,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1352550" y="9014761"/>
-          <a:ext cx="2667000" cy="947113"/>
+          <a:off x="1357993" y="8817457"/>
+          <a:ext cx="2688771" cy="919899"/>
           <a:chOff x="1358996" y="9612043"/>
           <a:chExt cx="2692781" cy="929925"/>
         </a:xfrm>
@@ -9890,14 +9890,14 @@
     <row r="41" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B41" s="32"/>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="N41" s="35"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B42" s="32"/>
       <c r="C42" s="40" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="N42" s="35"/>
     </row>
@@ -9942,27 +9942,27 @@
   <sheetData>
     <row r="1" spans="2:15" ht="30" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B9" s="41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -9986,7 +9986,7 @@
     </row>
     <row r="10" spans="2:15" ht="33" x14ac:dyDescent="0.4">
       <c r="B10" s="44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="45"/>
       <c r="D10" s="46"/>
@@ -10004,7 +10004,7 @@
     </row>
     <row r="11" spans="2:15" ht="33" x14ac:dyDescent="0.4">
       <c r="B11" s="44" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="46"/>
@@ -10038,11 +10038,11 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B13" s="44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" s="46"/>
       <c r="D13" s="46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
@@ -10060,7 +10060,7 @@
       <c r="B14" s="44"/>
       <c r="C14" s="46"/>
       <c r="D14" s="46" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" s="46"/>
       <c r="F14" s="46"/>
@@ -10078,7 +10078,7 @@
       <c r="B15" s="44"/>
       <c r="C15" s="46"/>
       <c r="D15" s="46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" s="46"/>
       <c r="F15" s="46"/>
@@ -10096,7 +10096,7 @@
       <c r="B16" s="44"/>
       <c r="C16" s="46"/>
       <c r="D16" s="46" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" s="46"/>
       <c r="F16" s="46"/>
@@ -10114,7 +10114,7 @@
       <c r="B17" s="44"/>
       <c r="C17" s="46"/>
       <c r="D17" s="46" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E17" s="46"/>
       <c r="F17" s="46"/>
@@ -10132,7 +10132,7 @@
       <c r="B18" s="44"/>
       <c r="C18" s="46"/>
       <c r="D18" s="46" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" s="46"/>
       <c r="F18" s="46"/>
@@ -10150,7 +10150,7 @@
       <c r="B19" s="44"/>
       <c r="C19" s="46"/>
       <c r="D19" s="46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E19" s="46"/>
       <c r="F19" s="46"/>
@@ -10168,7 +10168,7 @@
       <c r="B20" s="44"/>
       <c r="C20" s="46"/>
       <c r="D20" s="46" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20" s="46"/>
       <c r="F20" s="46"/>
@@ -10218,7 +10218,7 @@
       <c r="B23" s="44"/>
       <c r="C23" s="46"/>
       <c r="D23" s="46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E23" s="46"/>
       <c r="F23" s="46"/>
@@ -10236,7 +10236,7 @@
       <c r="B24" s="44"/>
       <c r="C24" s="46"/>
       <c r="D24" s="46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24" s="46"/>
       <c r="F24" s="46"/>
@@ -10254,7 +10254,7 @@
       <c r="B25" s="44"/>
       <c r="C25" s="46"/>
       <c r="D25" s="46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E25" s="46"/>
       <c r="F25" s="46"/>
@@ -10288,7 +10288,7 @@
       <c r="B27" s="48"/>
       <c r="C27" s="49"/>
       <c r="D27" s="49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27" s="49"/>
       <c r="F27" s="49"/>
@@ -10306,7 +10306,7 @@
       <c r="B28" s="48"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
@@ -10324,7 +10324,7 @@
       <c r="B29" s="48"/>
       <c r="C29" s="49"/>
       <c r="D29" s="49" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
@@ -10342,12 +10342,12 @@
       <c r="B30" s="48"/>
       <c r="C30" s="49"/>
       <c r="D30" s="49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E30" s="49"/>
       <c r="F30" s="49"/>
       <c r="G30" s="49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H30" s="49"/>
       <c r="I30" s="49"/>
@@ -10362,12 +10362,12 @@
       <c r="B31" s="48"/>
       <c r="C31" s="49"/>
       <c r="D31" s="49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E31" s="49"/>
       <c r="F31" s="49"/>
       <c r="G31" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H31" s="49"/>
       <c r="I31" s="49"/>
@@ -10382,12 +10382,12 @@
       <c r="B32" s="48"/>
       <c r="C32" s="49"/>
       <c r="D32" s="49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E32" s="49"/>
       <c r="F32" s="49"/>
       <c r="G32" s="49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H32" s="49"/>
       <c r="I32" s="49"/>
@@ -10418,7 +10418,7 @@
       <c r="B34" s="48"/>
       <c r="C34" s="49"/>
       <c r="D34" s="49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E34" s="49"/>
       <c r="F34" s="49"/>
@@ -10436,7 +10436,7 @@
       <c r="B35" s="48"/>
       <c r="C35" s="49"/>
       <c r="D35" s="49" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E35" s="49"/>
       <c r="F35" s="49"/>
@@ -10454,12 +10454,12 @@
       <c r="B36" s="48"/>
       <c r="C36" s="49"/>
       <c r="D36" s="49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E36" s="49"/>
       <c r="F36" s="49"/>
       <c r="G36" s="49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H36" s="49"/>
       <c r="I36" s="49"/>
@@ -10474,12 +10474,12 @@
       <c r="B37" s="48"/>
       <c r="C37" s="49"/>
       <c r="D37" s="49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E37" s="49"/>
       <c r="F37" s="49"/>
       <c r="G37" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
@@ -10494,12 +10494,12 @@
       <c r="B38" s="48"/>
       <c r="C38" s="49"/>
       <c r="D38" s="49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E38" s="49"/>
       <c r="F38" s="49"/>
       <c r="G38" s="49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H38" s="49"/>
       <c r="I38" s="49"/>
@@ -10530,7 +10530,7 @@
       <c r="B40" s="48"/>
       <c r="C40" s="49"/>
       <c r="D40" s="49" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E40" s="49"/>
       <c r="F40" s="49"/>
@@ -10548,12 +10548,12 @@
       <c r="B41" s="48"/>
       <c r="C41" s="49"/>
       <c r="D41" s="49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E41" s="49"/>
       <c r="F41" s="49"/>
       <c r="G41" s="49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="49"/>
@@ -10568,12 +10568,12 @@
       <c r="B42" s="48"/>
       <c r="C42" s="49"/>
       <c r="D42" s="49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E42" s="49"/>
       <c r="F42" s="49"/>
       <c r="G42" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="49"/>
@@ -10636,7 +10636,7 @@
       <c r="B46" s="48"/>
       <c r="C46" s="49"/>
       <c r="D46" s="49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E46" s="49"/>
       <c r="F46" s="49"/>
@@ -10654,7 +10654,7 @@
       <c r="B47" s="48"/>
       <c r="C47" s="49"/>
       <c r="D47" s="49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E47" s="49"/>
       <c r="F47" s="49"/>
@@ -10672,7 +10672,7 @@
       <c r="B48" s="48"/>
       <c r="C48" s="49"/>
       <c r="D48" s="49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E48" s="49"/>
       <c r="F48" s="49"/>
@@ -10722,7 +10722,7 @@
       <c r="B51" s="48"/>
       <c r="C51" s="49"/>
       <c r="D51" s="49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E51" s="49"/>
       <c r="F51" s="49"/>
@@ -10740,7 +10740,7 @@
       <c r="B52" s="48"/>
       <c r="C52" s="49"/>
       <c r="D52" s="49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E52" s="49"/>
       <c r="F52" s="49"/>
@@ -10822,7 +10822,7 @@
       <c r="B57" s="48"/>
       <c r="C57" s="49"/>
       <c r="D57" s="49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E57" s="49"/>
       <c r="F57" s="49"/>
@@ -10840,7 +10840,7 @@
       <c r="B58" s="48"/>
       <c r="C58" s="49"/>
       <c r="D58" s="49" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E58" s="49"/>
       <c r="F58" s="49"/>
@@ -10858,7 +10858,7 @@
       <c r="B59" s="48"/>
       <c r="C59" s="49"/>
       <c r="D59" s="49" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E59" s="49"/>
       <c r="F59" s="49"/>
@@ -10940,7 +10940,7 @@
       <c r="B64" s="48"/>
       <c r="C64" s="49"/>
       <c r="D64" s="49" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E64" s="49"/>
       <c r="F64" s="49"/>
@@ -10958,7 +10958,7 @@
       <c r="B65" s="48"/>
       <c r="C65" s="49"/>
       <c r="D65" s="49" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E65" s="49"/>
       <c r="F65" s="49"/>
@@ -10976,7 +10976,7 @@
       <c r="B66" s="48"/>
       <c r="C66" s="49"/>
       <c r="D66" s="49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E66" s="49"/>
       <c r="F66" s="49"/>
@@ -11058,7 +11058,7 @@
       <c r="B71" s="48"/>
       <c r="C71" s="49"/>
       <c r="D71" s="49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E71" s="49"/>
       <c r="F71" s="49"/>
@@ -11076,13 +11076,13 @@
       <c r="B72" s="48"/>
       <c r="C72" s="49"/>
       <c r="D72" s="49" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E72" s="49"/>
       <c r="F72" s="49"/>
       <c r="G72" s="49"/>
       <c r="H72" s="51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -11096,13 +11096,13 @@
       <c r="B73" s="48"/>
       <c r="C73" s="49"/>
       <c r="D73" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E73" s="49"/>
       <c r="F73" s="49"/>
       <c r="G73" s="49"/>
       <c r="H73" s="51" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I73" s="49"/>
       <c r="J73" s="49"/>
@@ -11116,13 +11116,13 @@
       <c r="B74" s="48"/>
       <c r="C74" s="49"/>
       <c r="D74" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E74" s="49"/>
       <c r="F74" s="49"/>
       <c r="G74" s="49"/>
       <c r="H74" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -11136,13 +11136,13 @@
       <c r="B75" s="48"/>
       <c r="C75" s="49"/>
       <c r="D75" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E75" s="49"/>
       <c r="F75" s="49"/>
       <c r="G75" s="49"/>
       <c r="H75" s="51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I75" s="49"/>
       <c r="J75" s="49"/>
@@ -11156,13 +11156,13 @@
       <c r="B76" s="48"/>
       <c r="C76" s="49"/>
       <c r="D76" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E76" s="49"/>
       <c r="F76" s="49"/>
       <c r="G76" s="49"/>
       <c r="H76" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I76" s="49"/>
       <c r="J76" s="49"/>
@@ -11176,13 +11176,13 @@
       <c r="B77" s="48"/>
       <c r="C77" s="49"/>
       <c r="D77" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E77" s="49"/>
       <c r="F77" s="49"/>
       <c r="G77" s="49"/>
       <c r="H77" s="51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I77" s="49"/>
       <c r="J77" s="49"/>
@@ -11196,13 +11196,13 @@
       <c r="B78" s="48"/>
       <c r="C78" s="49"/>
       <c r="D78" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E78" s="49"/>
       <c r="F78" s="49"/>
       <c r="G78" s="49"/>
       <c r="H78" s="51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I78" s="49"/>
       <c r="J78" s="49"/>
@@ -11216,13 +11216,13 @@
       <c r="B79" s="48"/>
       <c r="C79" s="49"/>
       <c r="D79" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E79" s="49"/>
       <c r="F79" s="49"/>
       <c r="G79" s="49"/>
       <c r="H79" s="51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I79" s="49"/>
       <c r="J79" s="49"/>
@@ -11236,13 +11236,13 @@
       <c r="B80" s="48"/>
       <c r="C80" s="49"/>
       <c r="D80" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E80" s="49"/>
       <c r="F80" s="49"/>
       <c r="G80" s="49"/>
       <c r="H80" s="51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I80" s="49"/>
       <c r="J80" s="49"/>
@@ -11256,13 +11256,13 @@
       <c r="B81" s="48"/>
       <c r="C81" s="49"/>
       <c r="D81" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E81" s="49"/>
       <c r="F81" s="49"/>
       <c r="G81" s="49"/>
       <c r="H81" s="51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I81" s="49"/>
       <c r="J81" s="49"/>
@@ -11276,13 +11276,13 @@
       <c r="B82" s="48"/>
       <c r="C82" s="49"/>
       <c r="D82" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E82" s="49"/>
       <c r="F82" s="49"/>
       <c r="G82" s="49"/>
       <c r="H82" s="51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I82" s="49"/>
       <c r="J82" s="49"/>
@@ -11296,13 +11296,13 @@
       <c r="B83" s="48"/>
       <c r="C83" s="49"/>
       <c r="D83" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E83" s="49"/>
       <c r="F83" s="49"/>
       <c r="G83" s="49"/>
       <c r="H83" s="51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I83" s="49"/>
       <c r="J83" s="49"/>
@@ -11316,13 +11316,13 @@
       <c r="B84" s="48"/>
       <c r="C84" s="49"/>
       <c r="D84" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E84" s="49"/>
       <c r="F84" s="49"/>
       <c r="G84" s="49"/>
       <c r="H84" s="51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I84" s="49"/>
       <c r="J84" s="49"/>
@@ -11336,13 +11336,13 @@
       <c r="B85" s="48"/>
       <c r="C85" s="49"/>
       <c r="D85" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E85" s="49"/>
       <c r="F85" s="49"/>
       <c r="G85" s="49"/>
       <c r="H85" s="51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I85" s="49"/>
       <c r="J85" s="49"/>
@@ -11356,13 +11356,13 @@
       <c r="B86" s="48"/>
       <c r="C86" s="49"/>
       <c r="D86" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E86" s="49"/>
       <c r="F86" s="49"/>
       <c r="G86" s="49"/>
       <c r="H86" s="51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I86" s="49"/>
       <c r="J86" s="49"/>
@@ -11376,13 +11376,13 @@
       <c r="B87" s="48"/>
       <c r="C87" s="49"/>
       <c r="D87" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E87" s="49"/>
       <c r="F87" s="49"/>
       <c r="G87" s="49"/>
       <c r="H87" s="51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I87" s="49"/>
       <c r="J87" s="49"/>
@@ -11396,13 +11396,13 @@
       <c r="B88" s="48"/>
       <c r="C88" s="49"/>
       <c r="D88" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E88" s="49"/>
       <c r="F88" s="49"/>
       <c r="G88" s="49"/>
       <c r="H88" s="51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I88" s="49"/>
       <c r="J88" s="49"/>
@@ -11416,13 +11416,13 @@
       <c r="B89" s="48"/>
       <c r="C89" s="49"/>
       <c r="D89" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E89" s="49"/>
       <c r="F89" s="49"/>
       <c r="G89" s="49"/>
       <c r="H89" s="51" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I89" s="49"/>
       <c r="J89" s="49"/>
@@ -11436,13 +11436,13 @@
       <c r="B90" s="48"/>
       <c r="C90" s="49"/>
       <c r="D90" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E90" s="49"/>
       <c r="F90" s="49"/>
       <c r="G90" s="49"/>
       <c r="H90" s="51" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I90" s="49"/>
       <c r="J90" s="49"/>
@@ -11456,13 +11456,13 @@
       <c r="B91" s="48"/>
       <c r="C91" s="49"/>
       <c r="D91" s="49" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E91" s="49"/>
       <c r="F91" s="49"/>
       <c r="G91" s="49"/>
       <c r="H91" s="51" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I91" s="49"/>
       <c r="J91" s="49"/>
@@ -11492,7 +11492,7 @@
       <c r="B93" s="48"/>
       <c r="C93" s="49"/>
       <c r="D93" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E93" s="49"/>
       <c r="F93" s="49"/>
@@ -11510,7 +11510,7 @@
       <c r="B94" s="48"/>
       <c r="C94" s="49"/>
       <c r="D94" s="49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E94" s="49"/>
       <c r="F94" s="49"/>
@@ -11560,7 +11560,7 @@
       <c r="B97" s="48"/>
       <c r="C97" s="49"/>
       <c r="D97" s="49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E97" s="49"/>
       <c r="F97" s="49"/>
@@ -11576,7 +11576,7 @@
     </row>
     <row r="98" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B98" s="48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C98" s="49"/>
       <c r="D98" s="49"/>

--- a/97_Mockup/Wire_Frame.xlsx
+++ b/97_Mockup/Wire_Frame.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\97_Mockup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD1580E-CE9B-48FB-A6A1-7D1CBBE4A881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCF4490-D742-421C-B02F-64BAA48FCB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{78629192-825E-4083-940A-C6F0AB98E91E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{78629192-825E-4083-940A-C6F0AB98E91E}"/>
   </bookViews>
   <sheets>
     <sheet name="JSON構文チェッカー" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="86">
   <si>
     <t>－</t>
     <phoneticPr fontId="1"/>
@@ -560,19 +560,148 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>資源一致件数：20件</t>
-    <rPh sb="0" eb="2">
-      <t>シゲン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケンスウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ケン</t>
-    </rPh>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>日、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="178"/>
+      </rPr>
+      <t>‏</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>11:02:40</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -639,7 +768,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>3</t>
+      <t>4</t>
     </r>
     <r>
       <rPr>
@@ -672,7 +801,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>17</t>
+      <t>16</t>
     </r>
     <r>
       <rPr>
@@ -784,7 +913,18 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>4</t>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
     </r>
     <r>
       <rPr>
@@ -817,7 +957,18 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>16</t>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
     </r>
     <r>
       <rPr>
@@ -861,7 +1012,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:40</t>
+      <t>11:02:41</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -973,7 +1124,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>15</t>
+      <t>17</t>
     </r>
     <r>
       <rPr>
@@ -1028,7 +1179,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:41</t>
+      <t>11:02:42</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -1140,7 +1291,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>17</t>
+      <t>18</t>
     </r>
     <r>
       <rPr>
@@ -1195,7 +1346,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:42</t>
+      <t>11:02:43</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
@@ -1307,7 +1458,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>18</t>
+      <t>17</t>
     </r>
     <r>
       <rPr>
@@ -1362,9 +1513,19 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:43</t>
-    </r>
-    <phoneticPr fontId="1"/>
+      <t>11:02:44</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
   </si>
   <si>
     <r>
@@ -1529,7 +1690,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:44</t>
+      <t>11:02:45</t>
     </r>
     <r>
       <rPr>
@@ -1706,7 +1867,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:45</t>
+      <t>11:02:46</t>
     </r>
     <r>
       <rPr>
@@ -1883,7 +2044,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:46</t>
+      <t>11:02:47</t>
     </r>
     <r>
       <rPr>
@@ -2060,7 +2221,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:47</t>
+      <t>11:02:48</t>
     </r>
     <r>
       <rPr>
@@ -2237,7 +2398,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:48</t>
+      <t>11:02:49</t>
     </r>
     <r>
       <rPr>
@@ -2414,7 +2575,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:49</t>
+      <t>11:02:50</t>
     </r>
     <r>
       <rPr>
@@ -2591,7 +2752,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:50</t>
+      <t>11:02:51</t>
     </r>
     <r>
       <rPr>
@@ -2768,7 +2929,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:51</t>
+      <t>11:02:52</t>
     </r>
     <r>
       <rPr>
@@ -2945,7 +3106,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:52</t>
+      <t>11:02:53</t>
     </r>
     <r>
       <rPr>
@@ -3122,7 +3283,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:53</t>
+      <t>11:02:54</t>
     </r>
     <r>
       <rPr>
@@ -3299,7 +3460,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:54</t>
+      <t>11:02:55</t>
     </r>
     <r>
       <rPr>
@@ -3476,7 +3637,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:55</t>
+      <t>11:02:56</t>
     </r>
     <r>
       <rPr>
@@ -3653,7 +3814,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:56</t>
+      <t>11:02:57</t>
     </r>
     <r>
       <rPr>
@@ -3830,7 +3991,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>11:02:57</t>
+      <t>11:02:58</t>
     </r>
     <r>
       <rPr>
@@ -3843,301 +4004,6 @@
       </rPr>
       <t/>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>17</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>日、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="178"/>
-      </rPr>
-      <t>‏</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>11:02:58</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>最終更新日時：2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4月</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>16日、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="178"/>
-      </rPr>
-      <t>‏</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>‎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11:02:40</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>サイシュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ニチジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
@@ -4263,6 +4129,255 @@
   </si>
   <si>
     <t>○○ディレクトリ２リンク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>最新アクセス日時：2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4月</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16日、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="178"/>
+      </rPr>
+      <t>‏</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11:02:40</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>最新更新日時　　：2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4月</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16日、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="178"/>
+      </rPr>
+      <t>‏</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‎</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11:02:40</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資源一致件数　　：20件</t>
+    <rPh sb="0" eb="2">
+      <t>シゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンスウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -9890,14 +10005,14 @@
     <row r="41" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B41" s="32"/>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N41" s="35"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B42" s="32"/>
       <c r="C42" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N42" s="35"/>
     </row>
@@ -11082,7 +11197,7 @@
       <c r="F72" s="49"/>
       <c r="G72" s="49"/>
       <c r="H72" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
@@ -11102,7 +11217,7 @@
       <c r="F73" s="49"/>
       <c r="G73" s="49"/>
       <c r="H73" s="51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I73" s="49"/>
       <c r="J73" s="49"/>
@@ -11122,7 +11237,7 @@
       <c r="F74" s="49"/>
       <c r="G74" s="49"/>
       <c r="H74" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
@@ -11142,7 +11257,7 @@
       <c r="F75" s="49"/>
       <c r="G75" s="49"/>
       <c r="H75" s="51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I75" s="49"/>
       <c r="J75" s="49"/>
@@ -11162,7 +11277,7 @@
       <c r="F76" s="49"/>
       <c r="G76" s="49"/>
       <c r="H76" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I76" s="49"/>
       <c r="J76" s="49"/>
@@ -11182,7 +11297,7 @@
       <c r="F77" s="49"/>
       <c r="G77" s="49"/>
       <c r="H77" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I77" s="49"/>
       <c r="J77" s="49"/>
@@ -11202,7 +11317,7 @@
       <c r="F78" s="49"/>
       <c r="G78" s="49"/>
       <c r="H78" s="51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I78" s="49"/>
       <c r="J78" s="49"/>
@@ -11222,7 +11337,7 @@
       <c r="F79" s="49"/>
       <c r="G79" s="49"/>
       <c r="H79" s="51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I79" s="49"/>
       <c r="J79" s="49"/>
@@ -11242,7 +11357,7 @@
       <c r="F80" s="49"/>
       <c r="G80" s="49"/>
       <c r="H80" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I80" s="49"/>
       <c r="J80" s="49"/>
@@ -11262,7 +11377,7 @@
       <c r="F81" s="49"/>
       <c r="G81" s="49"/>
       <c r="H81" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I81" s="49"/>
       <c r="J81" s="49"/>
@@ -11282,7 +11397,7 @@
       <c r="F82" s="49"/>
       <c r="G82" s="49"/>
       <c r="H82" s="51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I82" s="49"/>
       <c r="J82" s="49"/>
@@ -11302,7 +11417,7 @@
       <c r="F83" s="49"/>
       <c r="G83" s="49"/>
       <c r="H83" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I83" s="49"/>
       <c r="J83" s="49"/>
@@ -11322,7 +11437,7 @@
       <c r="F84" s="49"/>
       <c r="G84" s="49"/>
       <c r="H84" s="51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I84" s="49"/>
       <c r="J84" s="49"/>
@@ -11342,7 +11457,7 @@
       <c r="F85" s="49"/>
       <c r="G85" s="49"/>
       <c r="H85" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I85" s="49"/>
       <c r="J85" s="49"/>
@@ -11362,7 +11477,7 @@
       <c r="F86" s="49"/>
       <c r="G86" s="49"/>
       <c r="H86" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I86" s="49"/>
       <c r="J86" s="49"/>
@@ -11382,7 +11497,7 @@
       <c r="F87" s="49"/>
       <c r="G87" s="49"/>
       <c r="H87" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I87" s="49"/>
       <c r="J87" s="49"/>
@@ -11402,7 +11517,7 @@
       <c r="F88" s="49"/>
       <c r="G88" s="49"/>
       <c r="H88" s="51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I88" s="49"/>
       <c r="J88" s="49"/>
@@ -11422,7 +11537,7 @@
       <c r="F89" s="49"/>
       <c r="G89" s="49"/>
       <c r="H89" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I89" s="49"/>
       <c r="J89" s="49"/>
@@ -11442,7 +11557,7 @@
       <c r="F90" s="49"/>
       <c r="G90" s="49"/>
       <c r="H90" s="51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I90" s="49"/>
       <c r="J90" s="49"/>
@@ -11462,7 +11577,7 @@
       <c r="F91" s="49"/>
       <c r="G91" s="49"/>
       <c r="H91" s="51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I91" s="49"/>
       <c r="J91" s="49"/>
@@ -11492,7 +11607,7 @@
       <c r="B93" s="48"/>
       <c r="C93" s="49"/>
       <c r="D93" s="49" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E93" s="49"/>
       <c r="F93" s="49"/>
@@ -11510,7 +11625,7 @@
       <c r="B94" s="48"/>
       <c r="C94" s="49"/>
       <c r="D94" s="49" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E94" s="49"/>
       <c r="F94" s="49"/>
@@ -11527,7 +11642,9 @@
     <row r="95" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B95" s="48"/>
       <c r="C95" s="49"/>
-      <c r="D95" s="49"/>
+      <c r="D95" s="49" t="s">
+        <v>83</v>
+      </c>
       <c r="E95" s="49"/>
       <c r="F95" s="49"/>
       <c r="G95" s="49"/>
@@ -11560,7 +11677,7 @@
       <c r="B97" s="48"/>
       <c r="C97" s="49"/>
       <c r="D97" s="49" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E97" s="49"/>
       <c r="F97" s="49"/>

--- a/97_Mockup/Wire_Frame.xlsx
+++ b/97_Mockup/Wire_Frame.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\portfolio\97_Mockup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCF4490-D742-421C-B02F-64BAA48FCB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92776CDD-7C4A-4306-A907-ABAAAFD4C439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{78629192-825E-4083-940A-C6F0AB98E91E}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">JSON構文チェッカー!$A$1:$Q$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">ステータスチェック!$A$1:$Q$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">ステータスチェック!$A$1:$Q$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="99">
   <si>
     <t>－</t>
     <phoneticPr fontId="1"/>
@@ -376,16 +376,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve"> 5: 資源確認</t>
-    <rPh sb="4" eb="6">
-      <t>シゲン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>手動実行モードです。</t>
     <rPh sb="0" eb="2">
       <t>シュドウ</t>
@@ -4377,6 +4367,70 @@
     </rPh>
     <rPh sb="11" eb="12">
       <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【サービス】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Status   Name               DisplayName</t>
+  </si>
+  <si>
+    <t>------   ----               -----------</t>
+  </si>
+  <si>
+    <t>Running  TestService1            TestSer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Running  TestService2            TestSer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Name                                           Version</t>
+  </si>
+  <si>
+    <t>----                                           -------</t>
+  </si>
+  <si>
+    <t>【ストアアプリ】</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Framework.2.2             2.2.XXXXX.0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Runtime.2.2                  2.2.XXXXX.0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stop        TestService3            TestSer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6:サービス確認</t>
+    <rPh sb="7" eb="9">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5:ストアアプリバージョン確認</t>
+    <rPh sb="14" eb="16">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7: 資源確認</t>
+    <rPh sb="4" eb="6">
+      <t>シゲン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -9082,14 +9136,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>400051</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>142873</xdr:rowOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>20408</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9104,8 +9158,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6572251" y="22078948"/>
-          <a:ext cx="3724274" cy="1581152"/>
+          <a:off x="6523265" y="25737908"/>
+          <a:ext cx="3691617" cy="1816556"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
@@ -9221,13 +9275,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>85726</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>219073</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>119</xdr:row>
       <xdr:rowOff>200025</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -9314,6 +9368,803 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>5113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>183705</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="23" name="グループ化 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F510B62-EA99-5059-81C7-8F2C93C70422}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1894114" y="20824042"/>
+          <a:ext cx="7255329" cy="423520"/>
+          <a:chOff x="1143000" y="8581696"/>
+          <a:chExt cx="6086475" cy="409912"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="24" name="フリーフォーム: 図形 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12403818-0511-7AA7-ABDB-306EC38F26B7}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1143000" y="8581696"/>
+            <a:ext cx="6086475" cy="247987"/>
+          </a:xfrm>
+          <a:custGeom>
+            <a:avLst/>
+            <a:gdLst>
+              <a:gd name="csX0" fmla="*/ 0 w 6086475"/>
+              <a:gd name="csY0" fmla="*/ 19379 h 247987"/>
+              <a:gd name="csX1" fmla="*/ 657225 w 6086475"/>
+              <a:gd name="csY1" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX2" fmla="*/ 1371600 w 6086475"/>
+              <a:gd name="csY2" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX3" fmla="*/ 2038350 w 6086475"/>
+              <a:gd name="csY3" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX4" fmla="*/ 2705100 w 6086475"/>
+              <a:gd name="csY4" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX5" fmla="*/ 3409950 w 6086475"/>
+              <a:gd name="csY5" fmla="*/ 247979 h 247987"/>
+              <a:gd name="csX6" fmla="*/ 4086225 w 6086475"/>
+              <a:gd name="csY6" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX7" fmla="*/ 4829175 w 6086475"/>
+              <a:gd name="csY7" fmla="*/ 190829 h 247987"/>
+              <a:gd name="csX8" fmla="*/ 5372100 w 6086475"/>
+              <a:gd name="csY8" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX9" fmla="*/ 6086475 w 6086475"/>
+              <a:gd name="csY9" fmla="*/ 200354 h 247987"/>
+            </a:gdLst>
+            <a:ahLst/>
+            <a:cxnLst>
+              <a:cxn ang="0">
+                <a:pos x="csX0" y="csY0"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX1" y="csY1"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX2" y="csY2"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX3" y="csY3"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX4" y="csY4"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX5" y="csY5"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX6" y="csY6"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX7" y="csY7"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX8" y="csY8"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX9" y="csY9"/>
+              </a:cxn>
+            </a:cxnLst>
+            <a:rect l="l" t="t" r="r" b="b"/>
+            <a:pathLst>
+              <a:path w="6086475" h="247987">
+                <a:moveTo>
+                  <a:pt x="0" y="19379"/>
+                </a:moveTo>
+                <a:cubicBezTo>
+                  <a:pt x="214312" y="115422"/>
+                  <a:pt x="428625" y="211466"/>
+                  <a:pt x="657225" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="885825" y="208292"/>
+                  <a:pt x="1141413" y="9854"/>
+                  <a:pt x="1371600" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="1601787" y="9854"/>
+                  <a:pt x="1816100" y="209879"/>
+                  <a:pt x="2038350" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2260600" y="209879"/>
+                  <a:pt x="2476500" y="3504"/>
+                  <a:pt x="2705100" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2933700" y="16204"/>
+                  <a:pt x="3179763" y="249567"/>
+                  <a:pt x="3409950" y="247979"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="3640138" y="246392"/>
+                  <a:pt x="3849688" y="9854"/>
+                  <a:pt x="4086225" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="4322762" y="-9196"/>
+                  <a:pt x="4614863" y="190829"/>
+                  <a:pt x="4829175" y="190829"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5043487" y="190829"/>
+                  <a:pt x="5162550" y="-1259"/>
+                  <a:pt x="5372100" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5581650" y="1916"/>
+                  <a:pt x="5876925" y="205117"/>
+                  <a:pt x="6086475" y="200354"/>
+                </a:cubicBezTo>
+              </a:path>
+            </a:pathLst>
+          </a:custGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="25" name="フリーフォーム: 図形 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921BBB94-CFBE-22A4-AD12-8F28C4182BDE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1143000" y="8743621"/>
+            <a:ext cx="6086475" cy="247987"/>
+          </a:xfrm>
+          <a:custGeom>
+            <a:avLst/>
+            <a:gdLst>
+              <a:gd name="csX0" fmla="*/ 0 w 6086475"/>
+              <a:gd name="csY0" fmla="*/ 19379 h 247987"/>
+              <a:gd name="csX1" fmla="*/ 657225 w 6086475"/>
+              <a:gd name="csY1" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX2" fmla="*/ 1371600 w 6086475"/>
+              <a:gd name="csY2" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX3" fmla="*/ 2038350 w 6086475"/>
+              <a:gd name="csY3" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX4" fmla="*/ 2705100 w 6086475"/>
+              <a:gd name="csY4" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX5" fmla="*/ 3409950 w 6086475"/>
+              <a:gd name="csY5" fmla="*/ 247979 h 247987"/>
+              <a:gd name="csX6" fmla="*/ 4086225 w 6086475"/>
+              <a:gd name="csY6" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX7" fmla="*/ 4829175 w 6086475"/>
+              <a:gd name="csY7" fmla="*/ 190829 h 247987"/>
+              <a:gd name="csX8" fmla="*/ 5372100 w 6086475"/>
+              <a:gd name="csY8" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX9" fmla="*/ 6086475 w 6086475"/>
+              <a:gd name="csY9" fmla="*/ 200354 h 247987"/>
+            </a:gdLst>
+            <a:ahLst/>
+            <a:cxnLst>
+              <a:cxn ang="0">
+                <a:pos x="csX0" y="csY0"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX1" y="csY1"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX2" y="csY2"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX3" y="csY3"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX4" y="csY4"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX5" y="csY5"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX6" y="csY6"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX7" y="csY7"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX8" y="csY8"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX9" y="csY9"/>
+              </a:cxn>
+            </a:cxnLst>
+            <a:rect l="l" t="t" r="r" b="b"/>
+            <a:pathLst>
+              <a:path w="6086475" h="247987">
+                <a:moveTo>
+                  <a:pt x="0" y="19379"/>
+                </a:moveTo>
+                <a:cubicBezTo>
+                  <a:pt x="214312" y="115422"/>
+                  <a:pt x="428625" y="211466"/>
+                  <a:pt x="657225" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="885825" y="208292"/>
+                  <a:pt x="1141413" y="9854"/>
+                  <a:pt x="1371600" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="1601787" y="9854"/>
+                  <a:pt x="1816100" y="209879"/>
+                  <a:pt x="2038350" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2260600" y="209879"/>
+                  <a:pt x="2476500" y="3504"/>
+                  <a:pt x="2705100" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2933700" y="16204"/>
+                  <a:pt x="3179763" y="249567"/>
+                  <a:pt x="3409950" y="247979"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="3640138" y="246392"/>
+                  <a:pt x="3849688" y="9854"/>
+                  <a:pt x="4086225" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="4322762" y="-9196"/>
+                  <a:pt x="4614863" y="190829"/>
+                  <a:pt x="4829175" y="190829"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5043487" y="190829"/>
+                  <a:pt x="5162550" y="-1259"/>
+                  <a:pt x="5372100" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5581650" y="1916"/>
+                  <a:pt x="5876925" y="205117"/>
+                  <a:pt x="6086475" y="200354"/>
+                </a:cubicBezTo>
+              </a:path>
+            </a:pathLst>
+          </a:custGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>468087</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>210907</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>77561</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>68034</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="吹き出し: 角を丸めた四角形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6C34F14-2F5C-61E6-53A1-0FD2A9BDA5C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6591301" y="17845764"/>
+          <a:ext cx="3691617" cy="1816556"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -57038"/>
+            <a:gd name="adj2" fmla="val -9326"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+            <a:alpha val="70000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Windows</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>にインストールされているアプリのバージョンとサービスの起動状態を確認する。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>73149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>6812</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="22" name="グループ化 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9646FBAE-2417-CB71-8466-28AC6F6DA8FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1894114" y="18932649"/>
+          <a:ext cx="7255329" cy="423520"/>
+          <a:chOff x="1143000" y="8581696"/>
+          <a:chExt cx="6086475" cy="409912"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="27" name="フリーフォーム: 図形 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36346479-83BE-F7BF-F8DD-85D17B16AA4D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1143000" y="8581696"/>
+            <a:ext cx="6086475" cy="247987"/>
+          </a:xfrm>
+          <a:custGeom>
+            <a:avLst/>
+            <a:gdLst>
+              <a:gd name="csX0" fmla="*/ 0 w 6086475"/>
+              <a:gd name="csY0" fmla="*/ 19379 h 247987"/>
+              <a:gd name="csX1" fmla="*/ 657225 w 6086475"/>
+              <a:gd name="csY1" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX2" fmla="*/ 1371600 w 6086475"/>
+              <a:gd name="csY2" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX3" fmla="*/ 2038350 w 6086475"/>
+              <a:gd name="csY3" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX4" fmla="*/ 2705100 w 6086475"/>
+              <a:gd name="csY4" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX5" fmla="*/ 3409950 w 6086475"/>
+              <a:gd name="csY5" fmla="*/ 247979 h 247987"/>
+              <a:gd name="csX6" fmla="*/ 4086225 w 6086475"/>
+              <a:gd name="csY6" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX7" fmla="*/ 4829175 w 6086475"/>
+              <a:gd name="csY7" fmla="*/ 190829 h 247987"/>
+              <a:gd name="csX8" fmla="*/ 5372100 w 6086475"/>
+              <a:gd name="csY8" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX9" fmla="*/ 6086475 w 6086475"/>
+              <a:gd name="csY9" fmla="*/ 200354 h 247987"/>
+            </a:gdLst>
+            <a:ahLst/>
+            <a:cxnLst>
+              <a:cxn ang="0">
+                <a:pos x="csX0" y="csY0"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX1" y="csY1"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX2" y="csY2"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX3" y="csY3"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX4" y="csY4"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX5" y="csY5"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX6" y="csY6"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX7" y="csY7"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX8" y="csY8"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX9" y="csY9"/>
+              </a:cxn>
+            </a:cxnLst>
+            <a:rect l="l" t="t" r="r" b="b"/>
+            <a:pathLst>
+              <a:path w="6086475" h="247987">
+                <a:moveTo>
+                  <a:pt x="0" y="19379"/>
+                </a:moveTo>
+                <a:cubicBezTo>
+                  <a:pt x="214312" y="115422"/>
+                  <a:pt x="428625" y="211466"/>
+                  <a:pt x="657225" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="885825" y="208292"/>
+                  <a:pt x="1141413" y="9854"/>
+                  <a:pt x="1371600" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="1601787" y="9854"/>
+                  <a:pt x="1816100" y="209879"/>
+                  <a:pt x="2038350" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2260600" y="209879"/>
+                  <a:pt x="2476500" y="3504"/>
+                  <a:pt x="2705100" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2933700" y="16204"/>
+                  <a:pt x="3179763" y="249567"/>
+                  <a:pt x="3409950" y="247979"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="3640138" y="246392"/>
+                  <a:pt x="3849688" y="9854"/>
+                  <a:pt x="4086225" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="4322762" y="-9196"/>
+                  <a:pt x="4614863" y="190829"/>
+                  <a:pt x="4829175" y="190829"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5043487" y="190829"/>
+                  <a:pt x="5162550" y="-1259"/>
+                  <a:pt x="5372100" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5581650" y="1916"/>
+                  <a:pt x="5876925" y="205117"/>
+                  <a:pt x="6086475" y="200354"/>
+                </a:cubicBezTo>
+              </a:path>
+            </a:pathLst>
+          </a:custGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="28" name="フリーフォーム: 図形 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99098162-22DF-89DA-55E3-32DCFB225D8C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1143000" y="8743621"/>
+            <a:ext cx="6086475" cy="247987"/>
+          </a:xfrm>
+          <a:custGeom>
+            <a:avLst/>
+            <a:gdLst>
+              <a:gd name="csX0" fmla="*/ 0 w 6086475"/>
+              <a:gd name="csY0" fmla="*/ 19379 h 247987"/>
+              <a:gd name="csX1" fmla="*/ 657225 w 6086475"/>
+              <a:gd name="csY1" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX2" fmla="*/ 1371600 w 6086475"/>
+              <a:gd name="csY2" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX3" fmla="*/ 2038350 w 6086475"/>
+              <a:gd name="csY3" fmla="*/ 209879 h 247987"/>
+              <a:gd name="csX4" fmla="*/ 2705100 w 6086475"/>
+              <a:gd name="csY4" fmla="*/ 9854 h 247987"/>
+              <a:gd name="csX5" fmla="*/ 3409950 w 6086475"/>
+              <a:gd name="csY5" fmla="*/ 247979 h 247987"/>
+              <a:gd name="csX6" fmla="*/ 4086225 w 6086475"/>
+              <a:gd name="csY6" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX7" fmla="*/ 4829175 w 6086475"/>
+              <a:gd name="csY7" fmla="*/ 190829 h 247987"/>
+              <a:gd name="csX8" fmla="*/ 5372100 w 6086475"/>
+              <a:gd name="csY8" fmla="*/ 329 h 247987"/>
+              <a:gd name="csX9" fmla="*/ 6086475 w 6086475"/>
+              <a:gd name="csY9" fmla="*/ 200354 h 247987"/>
+            </a:gdLst>
+            <a:ahLst/>
+            <a:cxnLst>
+              <a:cxn ang="0">
+                <a:pos x="csX0" y="csY0"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX1" y="csY1"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX2" y="csY2"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX3" y="csY3"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX4" y="csY4"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX5" y="csY5"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX6" y="csY6"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX7" y="csY7"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX8" y="csY8"/>
+              </a:cxn>
+              <a:cxn ang="0">
+                <a:pos x="csX9" y="csY9"/>
+              </a:cxn>
+            </a:cxnLst>
+            <a:rect l="l" t="t" r="r" b="b"/>
+            <a:pathLst>
+              <a:path w="6086475" h="247987">
+                <a:moveTo>
+                  <a:pt x="0" y="19379"/>
+                </a:moveTo>
+                <a:cubicBezTo>
+                  <a:pt x="214312" y="115422"/>
+                  <a:pt x="428625" y="211466"/>
+                  <a:pt x="657225" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="885825" y="208292"/>
+                  <a:pt x="1141413" y="9854"/>
+                  <a:pt x="1371600" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="1601787" y="9854"/>
+                  <a:pt x="1816100" y="209879"/>
+                  <a:pt x="2038350" y="209879"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2260600" y="209879"/>
+                  <a:pt x="2476500" y="3504"/>
+                  <a:pt x="2705100" y="9854"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="2933700" y="16204"/>
+                  <a:pt x="3179763" y="249567"/>
+                  <a:pt x="3409950" y="247979"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="3640138" y="246392"/>
+                  <a:pt x="3849688" y="9854"/>
+                  <a:pt x="4086225" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="4322762" y="-9196"/>
+                  <a:pt x="4614863" y="190829"/>
+                  <a:pt x="4829175" y="190829"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5043487" y="190829"/>
+                  <a:pt x="5162550" y="-1259"/>
+                  <a:pt x="5372100" y="329"/>
+                </a:cubicBezTo>
+                <a:cubicBezTo>
+                  <a:pt x="5581650" y="1916"/>
+                  <a:pt x="5876925" y="205117"/>
+                  <a:pt x="6086475" y="200354"/>
+                </a:cubicBezTo>
+              </a:path>
+            </a:pathLst>
+          </a:custGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10005,14 +10856,14 @@
     <row r="41" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B41" s="32"/>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N41" s="35"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B42" s="32"/>
       <c r="C42" s="40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N42" s="35"/>
     </row>
@@ -10048,7 +10899,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O102"/>
+  <dimension ref="B1:O120"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -10283,7 +11134,7 @@
       <c r="B20" s="44"/>
       <c r="C20" s="46"/>
       <c r="D20" s="46" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="E20" s="46"/>
       <c r="F20" s="46"/>
@@ -10300,7 +11151,9 @@
     <row r="21" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B21" s="44"/>
       <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
+      <c r="D21" s="46" t="s">
+        <v>96</v>
+      </c>
       <c r="E21" s="46"/>
       <c r="F21" s="46"/>
       <c r="G21" s="46"/>
@@ -10316,7 +11169,9 @@
     <row r="22" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B22" s="44"/>
       <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
+      <c r="D22" s="46" t="s">
+        <v>98</v>
+      </c>
       <c r="E22" s="46"/>
       <c r="F22" s="46"/>
       <c r="G22" s="46"/>
@@ -10351,7 +11206,7 @@
       <c r="B24" s="44"/>
       <c r="C24" s="46"/>
       <c r="D24" s="46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="46"/>
       <c r="F24" s="46"/>
@@ -10369,7 +11224,7 @@
       <c r="B25" s="44"/>
       <c r="C25" s="46"/>
       <c r="D25" s="46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" s="46"/>
       <c r="F25" s="46"/>
@@ -10403,7 +11258,7 @@
       <c r="B27" s="48"/>
       <c r="C27" s="49"/>
       <c r="D27" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" s="49"/>
       <c r="F27" s="49"/>
@@ -10421,7 +11276,7 @@
       <c r="B28" s="48"/>
       <c r="C28" s="49"/>
       <c r="D28" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
@@ -10439,7 +11294,7 @@
       <c r="B29" s="48"/>
       <c r="C29" s="49"/>
       <c r="D29" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
@@ -10457,12 +11312,12 @@
       <c r="B30" s="48"/>
       <c r="C30" s="49"/>
       <c r="D30" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" s="49"/>
       <c r="F30" s="49"/>
       <c r="G30" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H30" s="49"/>
       <c r="I30" s="49"/>
@@ -10477,12 +11332,12 @@
       <c r="B31" s="48"/>
       <c r="C31" s="49"/>
       <c r="D31" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" s="49"/>
       <c r="F31" s="49"/>
       <c r="G31" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H31" s="49"/>
       <c r="I31" s="49"/>
@@ -10497,12 +11352,12 @@
       <c r="B32" s="48"/>
       <c r="C32" s="49"/>
       <c r="D32" s="49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="49"/>
       <c r="F32" s="49"/>
       <c r="G32" s="49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H32" s="49"/>
       <c r="I32" s="49"/>
@@ -10533,7 +11388,7 @@
       <c r="B34" s="48"/>
       <c r="C34" s="49"/>
       <c r="D34" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" s="49"/>
       <c r="F34" s="49"/>
@@ -10551,7 +11406,7 @@
       <c r="B35" s="48"/>
       <c r="C35" s="49"/>
       <c r="D35" s="49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E35" s="49"/>
       <c r="F35" s="49"/>
@@ -10569,12 +11424,12 @@
       <c r="B36" s="48"/>
       <c r="C36" s="49"/>
       <c r="D36" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36" s="49"/>
       <c r="F36" s="49"/>
       <c r="G36" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H36" s="49"/>
       <c r="I36" s="49"/>
@@ -10589,12 +11444,12 @@
       <c r="B37" s="48"/>
       <c r="C37" s="49"/>
       <c r="D37" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" s="49"/>
       <c r="F37" s="49"/>
       <c r="G37" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
@@ -10609,12 +11464,12 @@
       <c r="B38" s="48"/>
       <c r="C38" s="49"/>
       <c r="D38" s="49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E38" s="49"/>
       <c r="F38" s="49"/>
       <c r="G38" s="49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H38" s="49"/>
       <c r="I38" s="49"/>
@@ -10645,7 +11500,7 @@
       <c r="B40" s="48"/>
       <c r="C40" s="49"/>
       <c r="D40" s="49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" s="49"/>
       <c r="F40" s="49"/>
@@ -10663,12 +11518,12 @@
       <c r="B41" s="48"/>
       <c r="C41" s="49"/>
       <c r="D41" s="49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" s="49"/>
       <c r="F41" s="49"/>
       <c r="G41" s="49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H41" s="49"/>
       <c r="I41" s="49"/>
@@ -10683,12 +11538,12 @@
       <c r="B42" s="48"/>
       <c r="C42" s="49"/>
       <c r="D42" s="49" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E42" s="49"/>
       <c r="F42" s="49"/>
       <c r="G42" s="49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H42" s="49"/>
       <c r="I42" s="49"/>
@@ -10751,7 +11606,7 @@
       <c r="B46" s="48"/>
       <c r="C46" s="49"/>
       <c r="D46" s="49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E46" s="49"/>
       <c r="F46" s="49"/>
@@ -10769,7 +11624,7 @@
       <c r="B47" s="48"/>
       <c r="C47" s="49"/>
       <c r="D47" s="49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E47" s="49"/>
       <c r="F47" s="49"/>
@@ -10787,7 +11642,7 @@
       <c r="B48" s="48"/>
       <c r="C48" s="49"/>
       <c r="D48" s="49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E48" s="49"/>
       <c r="F48" s="49"/>
@@ -10837,7 +11692,7 @@
       <c r="B51" s="48"/>
       <c r="C51" s="49"/>
       <c r="D51" s="49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E51" s="49"/>
       <c r="F51" s="49"/>
@@ -10855,7 +11710,7 @@
       <c r="B52" s="48"/>
       <c r="C52" s="49"/>
       <c r="D52" s="49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E52" s="49"/>
       <c r="F52" s="49"/>
@@ -10937,7 +11792,7 @@
       <c r="B57" s="48"/>
       <c r="C57" s="49"/>
       <c r="D57" s="49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E57" s="49"/>
       <c r="F57" s="49"/>
@@ -10955,7 +11810,7 @@
       <c r="B58" s="48"/>
       <c r="C58" s="49"/>
       <c r="D58" s="49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E58" s="49"/>
       <c r="F58" s="49"/>
@@ -10973,7 +11828,7 @@
       <c r="B59" s="48"/>
       <c r="C59" s="49"/>
       <c r="D59" s="49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E59" s="49"/>
       <c r="F59" s="49"/>
@@ -11055,7 +11910,7 @@
       <c r="B64" s="48"/>
       <c r="C64" s="49"/>
       <c r="D64" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E64" s="49"/>
       <c r="F64" s="49"/>
@@ -11073,7 +11928,7 @@
       <c r="B65" s="48"/>
       <c r="C65" s="49"/>
       <c r="D65" s="49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E65" s="49"/>
       <c r="F65" s="49"/>
@@ -11091,7 +11946,7 @@
       <c r="B66" s="48"/>
       <c r="C66" s="49"/>
       <c r="D66" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E66" s="49"/>
       <c r="F66" s="49"/>
@@ -11173,7 +12028,7 @@
       <c r="B71" s="48"/>
       <c r="C71" s="49"/>
       <c r="D71" s="49" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E71" s="49"/>
       <c r="F71" s="49"/>
@@ -11191,14 +12046,12 @@
       <c r="B72" s="48"/>
       <c r="C72" s="49"/>
       <c r="D72" s="49" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="E72" s="49"/>
       <c r="F72" s="49"/>
       <c r="G72" s="49"/>
-      <c r="H72" s="51" t="s">
-        <v>60</v>
-      </c>
+      <c r="H72" s="49"/>
       <c r="I72" s="49"/>
       <c r="J72" s="49"/>
       <c r="K72" s="49"/>
@@ -11211,14 +12064,12 @@
       <c r="B73" s="48"/>
       <c r="C73" s="49"/>
       <c r="D73" s="49" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="E73" s="49"/>
       <c r="F73" s="49"/>
       <c r="G73" s="49"/>
-      <c r="H73" s="51" t="s">
-        <v>61</v>
-      </c>
+      <c r="H73" s="49"/>
       <c r="I73" s="49"/>
       <c r="J73" s="49"/>
       <c r="K73" s="49"/>
@@ -11231,14 +12082,12 @@
       <c r="B74" s="48"/>
       <c r="C74" s="49"/>
       <c r="D74" s="49" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E74" s="49"/>
       <c r="F74" s="49"/>
       <c r="G74" s="49"/>
-      <c r="H74" s="51" t="s">
-        <v>62</v>
-      </c>
+      <c r="H74" s="49"/>
       <c r="I74" s="49"/>
       <c r="J74" s="49"/>
       <c r="K74" s="49"/>
@@ -11251,14 +12100,12 @@
       <c r="B75" s="48"/>
       <c r="C75" s="49"/>
       <c r="D75" s="49" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="E75" s="49"/>
       <c r="F75" s="49"/>
       <c r="G75" s="49"/>
-      <c r="H75" s="51" t="s">
-        <v>63</v>
-      </c>
+      <c r="H75" s="49"/>
       <c r="I75" s="49"/>
       <c r="J75" s="49"/>
       <c r="K75" s="49"/>
@@ -11271,14 +12118,12 @@
       <c r="B76" s="48"/>
       <c r="C76" s="49"/>
       <c r="D76" s="49" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E76" s="49"/>
       <c r="F76" s="49"/>
       <c r="G76" s="49"/>
-      <c r="H76" s="51" t="s">
-        <v>64</v>
-      </c>
+      <c r="H76" s="49"/>
       <c r="I76" s="49"/>
       <c r="J76" s="49"/>
       <c r="K76" s="49"/>
@@ -11290,15 +12135,11 @@
     <row r="77" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B77" s="48"/>
       <c r="C77" s="49"/>
-      <c r="D77" s="49" t="s">
-        <v>59</v>
-      </c>
+      <c r="D77" s="49"/>
       <c r="E77" s="49"/>
       <c r="F77" s="49"/>
       <c r="G77" s="49"/>
-      <c r="H77" s="51" t="s">
-        <v>65</v>
-      </c>
+      <c r="H77" s="49"/>
       <c r="I77" s="49"/>
       <c r="J77" s="49"/>
       <c r="K77" s="49"/>
@@ -11311,14 +12152,12 @@
       <c r="B78" s="48"/>
       <c r="C78" s="49"/>
       <c r="D78" s="49" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E78" s="49"/>
       <c r="F78" s="49"/>
       <c r="G78" s="49"/>
-      <c r="H78" s="51" t="s">
-        <v>66</v>
-      </c>
+      <c r="H78" s="49"/>
       <c r="I78" s="49"/>
       <c r="J78" s="49"/>
       <c r="K78" s="49"/>
@@ -11331,14 +12170,12 @@
       <c r="B79" s="48"/>
       <c r="C79" s="49"/>
       <c r="D79" s="49" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="E79" s="49"/>
       <c r="F79" s="49"/>
       <c r="G79" s="49"/>
-      <c r="H79" s="51" t="s">
-        <v>67</v>
-      </c>
+      <c r="H79" s="49"/>
       <c r="I79" s="49"/>
       <c r="J79" s="49"/>
       <c r="K79" s="49"/>
@@ -11351,14 +12188,12 @@
       <c r="B80" s="48"/>
       <c r="C80" s="49"/>
       <c r="D80" s="49" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="E80" s="49"/>
       <c r="F80" s="49"/>
       <c r="G80" s="49"/>
-      <c r="H80" s="51" t="s">
-        <v>68</v>
-      </c>
+      <c r="H80" s="49"/>
       <c r="I80" s="49"/>
       <c r="J80" s="49"/>
       <c r="K80" s="49"/>
@@ -11371,14 +12206,12 @@
       <c r="B81" s="48"/>
       <c r="C81" s="49"/>
       <c r="D81" s="49" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E81" s="49"/>
       <c r="F81" s="49"/>
       <c r="G81" s="49"/>
-      <c r="H81" s="51" t="s">
-        <v>69</v>
-      </c>
+      <c r="H81" s="49"/>
       <c r="I81" s="49"/>
       <c r="J81" s="49"/>
       <c r="K81" s="49"/>
@@ -11391,14 +12224,12 @@
       <c r="B82" s="48"/>
       <c r="C82" s="49"/>
       <c r="D82" s="49" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E82" s="49"/>
       <c r="F82" s="49"/>
       <c r="G82" s="49"/>
-      <c r="H82" s="51" t="s">
-        <v>70</v>
-      </c>
+      <c r="H82" s="49"/>
       <c r="I82" s="49"/>
       <c r="J82" s="49"/>
       <c r="K82" s="49"/>
@@ -11411,14 +12242,12 @@
       <c r="B83" s="48"/>
       <c r="C83" s="49"/>
       <c r="D83" s="49" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="E83" s="49"/>
       <c r="F83" s="49"/>
       <c r="G83" s="49"/>
-      <c r="H83" s="51" t="s">
-        <v>71</v>
-      </c>
+      <c r="H83" s="49"/>
       <c r="I83" s="49"/>
       <c r="J83" s="49"/>
       <c r="K83" s="49"/>
@@ -11430,15 +12259,11 @@
     <row r="84" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B84" s="48"/>
       <c r="C84" s="49"/>
-      <c r="D84" s="49" t="s">
-        <v>59</v>
-      </c>
+      <c r="D84" s="49"/>
       <c r="E84" s="49"/>
       <c r="F84" s="49"/>
       <c r="G84" s="49"/>
-      <c r="H84" s="51" t="s">
-        <v>72</v>
-      </c>
+      <c r="H84" s="49"/>
       <c r="I84" s="49"/>
       <c r="J84" s="49"/>
       <c r="K84" s="49"/>
@@ -11450,15 +12275,11 @@
     <row r="85" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B85" s="48"/>
       <c r="C85" s="49"/>
-      <c r="D85" s="49" t="s">
-        <v>59</v>
-      </c>
+      <c r="D85" s="49"/>
       <c r="E85" s="49"/>
       <c r="F85" s="49"/>
       <c r="G85" s="49"/>
-      <c r="H85" s="51" t="s">
-        <v>73</v>
-      </c>
+      <c r="H85" s="49"/>
       <c r="I85" s="49"/>
       <c r="J85" s="49"/>
       <c r="K85" s="49"/>
@@ -11471,14 +12292,12 @@
       <c r="B86" s="48"/>
       <c r="C86" s="49"/>
       <c r="D86" s="49" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E86" s="49"/>
       <c r="F86" s="49"/>
       <c r="G86" s="49"/>
-      <c r="H86" s="51" t="s">
-        <v>74</v>
-      </c>
+      <c r="H86" s="49"/>
       <c r="I86" s="49"/>
       <c r="J86" s="49"/>
       <c r="K86" s="49"/>
@@ -11491,13 +12310,13 @@
       <c r="B87" s="48"/>
       <c r="C87" s="49"/>
       <c r="D87" s="49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E87" s="49"/>
       <c r="F87" s="49"/>
       <c r="G87" s="49"/>
       <c r="H87" s="51" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="I87" s="49"/>
       <c r="J87" s="49"/>
@@ -11511,13 +12330,13 @@
       <c r="B88" s="48"/>
       <c r="C88" s="49"/>
       <c r="D88" s="49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E88" s="49"/>
       <c r="F88" s="49"/>
       <c r="G88" s="49"/>
       <c r="H88" s="51" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I88" s="49"/>
       <c r="J88" s="49"/>
@@ -11531,13 +12350,13 @@
       <c r="B89" s="48"/>
       <c r="C89" s="49"/>
       <c r="D89" s="49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E89" s="49"/>
       <c r="F89" s="49"/>
       <c r="G89" s="49"/>
       <c r="H89" s="51" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I89" s="49"/>
       <c r="J89" s="49"/>
@@ -11551,13 +12370,13 @@
       <c r="B90" s="48"/>
       <c r="C90" s="49"/>
       <c r="D90" s="49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E90" s="49"/>
       <c r="F90" s="49"/>
       <c r="G90" s="49"/>
       <c r="H90" s="51" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I90" s="49"/>
       <c r="J90" s="49"/>
@@ -11571,13 +12390,13 @@
       <c r="B91" s="48"/>
       <c r="C91" s="49"/>
       <c r="D91" s="49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E91" s="49"/>
       <c r="F91" s="49"/>
       <c r="G91" s="49"/>
       <c r="H91" s="51" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="I91" s="49"/>
       <c r="J91" s="49"/>
@@ -11590,11 +12409,15 @@
     <row r="92" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B92" s="48"/>
       <c r="C92" s="49"/>
-      <c r="D92" s="49"/>
+      <c r="D92" s="49" t="s">
+        <v>58</v>
+      </c>
       <c r="E92" s="49"/>
       <c r="F92" s="49"/>
       <c r="G92" s="49"/>
-      <c r="H92" s="49"/>
+      <c r="H92" s="51" t="s">
+        <v>64</v>
+      </c>
       <c r="I92" s="49"/>
       <c r="J92" s="49"/>
       <c r="K92" s="49"/>
@@ -11607,12 +12430,14 @@
       <c r="B93" s="48"/>
       <c r="C93" s="49"/>
       <c r="D93" s="49" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E93" s="49"/>
       <c r="F93" s="49"/>
       <c r="G93" s="49"/>
-      <c r="H93" s="49"/>
+      <c r="H93" s="51" t="s">
+        <v>65</v>
+      </c>
       <c r="I93" s="49"/>
       <c r="J93" s="49"/>
       <c r="K93" s="49"/>
@@ -11625,12 +12450,14 @@
       <c r="B94" s="48"/>
       <c r="C94" s="49"/>
       <c r="D94" s="49" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E94" s="49"/>
       <c r="F94" s="49"/>
       <c r="G94" s="49"/>
-      <c r="H94" s="49"/>
+      <c r="H94" s="51" t="s">
+        <v>66</v>
+      </c>
       <c r="I94" s="49"/>
       <c r="J94" s="49"/>
       <c r="K94" s="49"/>
@@ -11643,12 +12470,14 @@
       <c r="B95" s="48"/>
       <c r="C95" s="49"/>
       <c r="D95" s="49" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E95" s="49"/>
       <c r="F95" s="49"/>
       <c r="G95" s="49"/>
-      <c r="H95" s="49"/>
+      <c r="H95" s="51" t="s">
+        <v>67</v>
+      </c>
       <c r="I95" s="49"/>
       <c r="J95" s="49"/>
       <c r="K95" s="49"/>
@@ -11660,11 +12489,15 @@
     <row r="96" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B96" s="48"/>
       <c r="C96" s="49"/>
-      <c r="D96" s="49"/>
+      <c r="D96" s="49" t="s">
+        <v>58</v>
+      </c>
       <c r="E96" s="49"/>
       <c r="F96" s="49"/>
       <c r="G96" s="49"/>
-      <c r="H96" s="49"/>
+      <c r="H96" s="51" t="s">
+        <v>68</v>
+      </c>
       <c r="I96" s="49"/>
       <c r="J96" s="49"/>
       <c r="K96" s="49"/>
@@ -11677,12 +12510,14 @@
       <c r="B97" s="48"/>
       <c r="C97" s="49"/>
       <c r="D97" s="49" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E97" s="49"/>
       <c r="F97" s="49"/>
       <c r="G97" s="49"/>
-      <c r="H97" s="49"/>
+      <c r="H97" s="51" t="s">
+        <v>69</v>
+      </c>
       <c r="I97" s="49"/>
       <c r="J97" s="49"/>
       <c r="K97" s="49"/>
@@ -11692,15 +12527,17 @@
       <c r="O97" s="50"/>
     </row>
     <row r="98" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B98" s="48" t="s">
-        <v>27</v>
-      </c>
+      <c r="B98" s="48"/>
       <c r="C98" s="49"/>
-      <c r="D98" s="49"/>
+      <c r="D98" s="49" t="s">
+        <v>58</v>
+      </c>
       <c r="E98" s="49"/>
       <c r="F98" s="49"/>
       <c r="G98" s="49"/>
-      <c r="H98" s="49"/>
+      <c r="H98" s="51" t="s">
+        <v>70</v>
+      </c>
       <c r="I98" s="49"/>
       <c r="J98" s="49"/>
       <c r="K98" s="49"/>
@@ -11712,11 +12549,15 @@
     <row r="99" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B99" s="48"/>
       <c r="C99" s="49"/>
-      <c r="D99" s="49"/>
+      <c r="D99" s="49" t="s">
+        <v>58</v>
+      </c>
       <c r="E99" s="49"/>
       <c r="F99" s="49"/>
       <c r="G99" s="49"/>
-      <c r="H99" s="49"/>
+      <c r="H99" s="51" t="s">
+        <v>71</v>
+      </c>
       <c r="I99" s="49"/>
       <c r="J99" s="49"/>
       <c r="K99" s="49"/>
@@ -11728,11 +12569,15 @@
     <row r="100" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B100" s="48"/>
       <c r="C100" s="49"/>
-      <c r="D100" s="49"/>
+      <c r="D100" s="49" t="s">
+        <v>58</v>
+      </c>
       <c r="E100" s="49"/>
       <c r="F100" s="49"/>
       <c r="G100" s="49"/>
-      <c r="H100" s="49"/>
+      <c r="H100" s="51" t="s">
+        <v>72</v>
+      </c>
       <c r="I100" s="49"/>
       <c r="J100" s="49"/>
       <c r="K100" s="49"/>
@@ -11744,11 +12589,15 @@
     <row r="101" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B101" s="48"/>
       <c r="C101" s="49"/>
-      <c r="D101" s="49"/>
+      <c r="D101" s="49" t="s">
+        <v>58</v>
+      </c>
       <c r="E101" s="49"/>
       <c r="F101" s="49"/>
       <c r="G101" s="49"/>
-      <c r="H101" s="49"/>
+      <c r="H101" s="51" t="s">
+        <v>73</v>
+      </c>
       <c r="I101" s="49"/>
       <c r="J101" s="49"/>
       <c r="K101" s="49"/>
@@ -11758,20 +12607,338 @@
       <c r="O101" s="50"/>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B102" s="52"/>
-      <c r="C102" s="53"/>
-      <c r="D102" s="53"/>
-      <c r="E102" s="53"/>
-      <c r="F102" s="53"/>
-      <c r="G102" s="53"/>
-      <c r="H102" s="53"/>
-      <c r="I102" s="53"/>
-      <c r="J102" s="53"/>
-      <c r="K102" s="53"/>
-      <c r="L102" s="53"/>
-      <c r="M102" s="53"/>
-      <c r="N102" s="53"/>
-      <c r="O102" s="54"/>
+      <c r="B102" s="48"/>
+      <c r="C102" s="49"/>
+      <c r="D102" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E102" s="49"/>
+      <c r="F102" s="49"/>
+      <c r="G102" s="49"/>
+      <c r="H102" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="I102" s="49"/>
+      <c r="J102" s="49"/>
+      <c r="K102" s="49"/>
+      <c r="L102" s="49"/>
+      <c r="M102" s="49"/>
+      <c r="N102" s="49"/>
+      <c r="O102" s="50"/>
+    </row>
+    <row r="103" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B103" s="48"/>
+      <c r="C103" s="49"/>
+      <c r="D103" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E103" s="49"/>
+      <c r="F103" s="49"/>
+      <c r="G103" s="49"/>
+      <c r="H103" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I103" s="49"/>
+      <c r="J103" s="49"/>
+      <c r="K103" s="49"/>
+      <c r="L103" s="49"/>
+      <c r="M103" s="49"/>
+      <c r="N103" s="49"/>
+      <c r="O103" s="50"/>
+    </row>
+    <row r="104" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B104" s="48"/>
+      <c r="C104" s="49"/>
+      <c r="D104" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E104" s="49"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="49"/>
+      <c r="H104" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="I104" s="49"/>
+      <c r="J104" s="49"/>
+      <c r="K104" s="49"/>
+      <c r="L104" s="49"/>
+      <c r="M104" s="49"/>
+      <c r="N104" s="49"/>
+      <c r="O104" s="50"/>
+    </row>
+    <row r="105" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B105" s="48"/>
+      <c r="C105" s="49"/>
+      <c r="D105" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
+      <c r="G105" s="49"/>
+      <c r="H105" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="I105" s="49"/>
+      <c r="J105" s="49"/>
+      <c r="K105" s="49"/>
+      <c r="L105" s="49"/>
+      <c r="M105" s="49"/>
+      <c r="N105" s="49"/>
+      <c r="O105" s="50"/>
+    </row>
+    <row r="106" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B106" s="48"/>
+      <c r="C106" s="49"/>
+      <c r="D106" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E106" s="49"/>
+      <c r="F106" s="49"/>
+      <c r="G106" s="49"/>
+      <c r="H106" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="I106" s="49"/>
+      <c r="J106" s="49"/>
+      <c r="K106" s="49"/>
+      <c r="L106" s="49"/>
+      <c r="M106" s="49"/>
+      <c r="N106" s="49"/>
+      <c r="O106" s="50"/>
+    </row>
+    <row r="107" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B107" s="48"/>
+      <c r="C107" s="49"/>
+      <c r="D107" s="49"/>
+      <c r="E107" s="49"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="49"/>
+      <c r="H107" s="49"/>
+      <c r="I107" s="49"/>
+      <c r="J107" s="49"/>
+      <c r="K107" s="49"/>
+      <c r="L107" s="49"/>
+      <c r="M107" s="49"/>
+      <c r="N107" s="49"/>
+      <c r="O107" s="50"/>
+    </row>
+    <row r="108" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B108" s="48"/>
+      <c r="C108" s="49"/>
+      <c r="D108" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="E108" s="49"/>
+      <c r="F108" s="49"/>
+      <c r="G108" s="49"/>
+      <c r="H108" s="49"/>
+      <c r="I108" s="49"/>
+      <c r="J108" s="49"/>
+      <c r="K108" s="49"/>
+      <c r="L108" s="49"/>
+      <c r="M108" s="49"/>
+      <c r="N108" s="49"/>
+      <c r="O108" s="50"/>
+    </row>
+    <row r="109" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B109" s="48"/>
+      <c r="C109" s="49"/>
+      <c r="D109" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="49"/>
+      <c r="H109" s="49"/>
+      <c r="I109" s="49"/>
+      <c r="J109" s="49"/>
+      <c r="K109" s="49"/>
+      <c r="L109" s="49"/>
+      <c r="M109" s="49"/>
+      <c r="N109" s="49"/>
+      <c r="O109" s="50"/>
+    </row>
+    <row r="110" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B110" s="48"/>
+      <c r="C110" s="49"/>
+      <c r="D110" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="E110" s="49"/>
+      <c r="F110" s="49"/>
+      <c r="G110" s="49"/>
+      <c r="H110" s="49"/>
+      <c r="I110" s="49"/>
+      <c r="J110" s="49"/>
+      <c r="K110" s="49"/>
+      <c r="L110" s="49"/>
+      <c r="M110" s="49"/>
+      <c r="N110" s="49"/>
+      <c r="O110" s="50"/>
+    </row>
+    <row r="111" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B111" s="48"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="49"/>
+      <c r="H111" s="49"/>
+      <c r="I111" s="49"/>
+      <c r="J111" s="49"/>
+      <c r="K111" s="49"/>
+      <c r="L111" s="49"/>
+      <c r="M111" s="49"/>
+      <c r="N111" s="49"/>
+      <c r="O111" s="50"/>
+    </row>
+    <row r="112" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B112" s="48"/>
+      <c r="C112" s="49"/>
+      <c r="D112" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E112" s="49"/>
+      <c r="F112" s="49"/>
+      <c r="G112" s="49"/>
+      <c r="H112" s="49"/>
+      <c r="I112" s="49"/>
+      <c r="J112" s="49"/>
+      <c r="K112" s="49"/>
+      <c r="L112" s="49"/>
+      <c r="M112" s="49"/>
+      <c r="N112" s="49"/>
+      <c r="O112" s="50"/>
+    </row>
+    <row r="113" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B113" s="48"/>
+      <c r="C113" s="49"/>
+      <c r="D113" s="49"/>
+      <c r="E113" s="49"/>
+      <c r="F113" s="49"/>
+      <c r="G113" s="49"/>
+      <c r="H113" s="49"/>
+      <c r="I113" s="49"/>
+      <c r="J113" s="49"/>
+      <c r="K113" s="49"/>
+      <c r="L113" s="49"/>
+      <c r="M113" s="49"/>
+      <c r="N113" s="49"/>
+      <c r="O113" s="50"/>
+    </row>
+    <row r="114" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B114" s="48"/>
+      <c r="C114" s="49"/>
+      <c r="D114" s="49"/>
+      <c r="E114" s="49"/>
+      <c r="F114" s="49"/>
+      <c r="G114" s="49"/>
+      <c r="H114" s="49"/>
+      <c r="I114" s="49"/>
+      <c r="J114" s="49"/>
+      <c r="K114" s="49"/>
+      <c r="L114" s="49"/>
+      <c r="M114" s="49"/>
+      <c r="N114" s="49"/>
+      <c r="O114" s="50"/>
+    </row>
+    <row r="115" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B115" s="48"/>
+      <c r="C115" s="49"/>
+      <c r="D115" s="49"/>
+      <c r="E115" s="49"/>
+      <c r="F115" s="49"/>
+      <c r="G115" s="49"/>
+      <c r="H115" s="49"/>
+      <c r="I115" s="49"/>
+      <c r="J115" s="49"/>
+      <c r="K115" s="49"/>
+      <c r="L115" s="49"/>
+      <c r="M115" s="49"/>
+      <c r="N115" s="49"/>
+      <c r="O115" s="50"/>
+    </row>
+    <row r="116" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B116" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116" s="49"/>
+      <c r="D116" s="49"/>
+      <c r="E116" s="49"/>
+      <c r="F116" s="49"/>
+      <c r="G116" s="49"/>
+      <c r="H116" s="49"/>
+      <c r="I116" s="49"/>
+      <c r="J116" s="49"/>
+      <c r="K116" s="49"/>
+      <c r="L116" s="49"/>
+      <c r="M116" s="49"/>
+      <c r="N116" s="49"/>
+      <c r="O116" s="50"/>
+    </row>
+    <row r="117" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B117" s="48"/>
+      <c r="C117" s="49"/>
+      <c r="D117" s="49"/>
+      <c r="E117" s="49"/>
+      <c r="F117" s="49"/>
+      <c r="G117" s="49"/>
+      <c r="H117" s="49"/>
+      <c r="I117" s="49"/>
+      <c r="J117" s="49"/>
+      <c r="K117" s="49"/>
+      <c r="L117" s="49"/>
+      <c r="M117" s="49"/>
+      <c r="N117" s="49"/>
+      <c r="O117" s="50"/>
+    </row>
+    <row r="118" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B118" s="48"/>
+      <c r="C118" s="49"/>
+      <c r="D118" s="49"/>
+      <c r="E118" s="49"/>
+      <c r="F118" s="49"/>
+      <c r="G118" s="49"/>
+      <c r="H118" s="49"/>
+      <c r="I118" s="49"/>
+      <c r="J118" s="49"/>
+      <c r="K118" s="49"/>
+      <c r="L118" s="49"/>
+      <c r="M118" s="49"/>
+      <c r="N118" s="49"/>
+      <c r="O118" s="50"/>
+    </row>
+    <row r="119" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B119" s="48"/>
+      <c r="C119" s="49"/>
+      <c r="D119" s="49"/>
+      <c r="E119" s="49"/>
+      <c r="F119" s="49"/>
+      <c r="G119" s="49"/>
+      <c r="H119" s="49"/>
+      <c r="I119" s="49"/>
+      <c r="J119" s="49"/>
+      <c r="K119" s="49"/>
+      <c r="L119" s="49"/>
+      <c r="M119" s="49"/>
+      <c r="N119" s="49"/>
+      <c r="O119" s="50"/>
+    </row>
+    <row r="120" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B120" s="52"/>
+      <c r="C120" s="53"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="53"/>
+      <c r="F120" s="53"/>
+      <c r="G120" s="53"/>
+      <c r="H120" s="53"/>
+      <c r="I120" s="53"/>
+      <c r="J120" s="53"/>
+      <c r="K120" s="53"/>
+      <c r="L120" s="53"/>
+      <c r="M120" s="53"/>
+      <c r="N120" s="53"/>
+      <c r="O120" s="54"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
